--- a/important_mails_2026-08-20.xlsx
+++ b/important_mails_2026-08-20.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H367"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,21 +500,74 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 04:58:18 +0000</t>
+          <t>Thu, 20 Aug 2026 15:24:40 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>FBA reimbursement notification</t>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID OTe/t6gOEA
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on August 21, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-334253779112132</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 04:58:18 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -530,39 +583,192 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 16:05:40 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement attempted
+Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
+On 08/20/26 16:05 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
+ 420.18.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon Store,
+Amazon Services
+Help us improve your payment experience on Amaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 16:03:47 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 08/20/26 16:03 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 1.195,03.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 16:03:34 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 08/20/26 16:03 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
+ 1042.32.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Am</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 12:23:03 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>You're exactly who Accelerate was designed for</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-18/7z58zcm/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
 [Your next level starts here](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58zcq/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
@@ -577,39 +783,134 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 14:31:59 +0000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Pagamento elaborato con successo</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+This title will display on mobile devices
+ Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
+ Tentativo di pagamento
+Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
+In data 08/20/26 14:31 CEST, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
+ 235,47.
+ Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
+ Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
+ Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 20:05:47 +0000</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon-Fulfilled Inventory</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
+You were required to submit a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choice within 30 days of the notification sent on 20/07/2026. Since no removal order was submitted since the notification was sent, we have submitted a disposal order for this inventory in accordance with our FBA policies.
+For more information regarding the removal of your product(s), see the notification e-mail you received from our Seller Performance Team. If you have any further questions, please contact our Seller Support .
+Thank you for your attention to this matter.
+Yours faithfully,
+Fulfilment by Amazon Team
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0F23SWF2P
+ SPC-EUAmazon-1055532845992348</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Wed, 19 Aug 2026 16:12:03 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -630,39 +931,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 05:03:01 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -678,39 +979,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 04:53:18 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -726,39 +1027,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sun, 16 Aug 2026 04:55:15 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -774,39 +1075,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 16 Aug 2026 02:33:51 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (TGTg3P+M9T)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -831,39 +1132,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -879,39 +1180,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 04:42:49 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -927,39 +1228,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 01:29:59 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -980,40 +1281,40 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Live at Accelerate 2026: Mary Beth Westmoreland and Amit Agarwal
  fireside chat</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bxx/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58by1/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
@@ -1026,39 +1327,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:27:13 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1075,39 +1376,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:26:45 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1127,39 +1428,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:39:43 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1179,39 +1480,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:38:59 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1228,39 +1529,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 10:11:50 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1277,39 +1578,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 10:11:23 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1329,39 +1630,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 07:03:07 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>您的亚马逊卖家账户支付的余额</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
 您的亚马逊卖家账户支付的余额
@@ -1390,39 +1691,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 10:06:05 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -1449,89 +1750,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 13 Aug 2026 16:08:49 +0000</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Submit product safety documentation to reactivate listings
- Hello Weihai CA,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 00:28:18 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>通过 Q4 活动拓展您的业务 — 尽早提报，节省费用</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Q4 业绩
 尊敬的卖家，
@@ -1561,39 +1812,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:40:40 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1608,39 +1859,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:39:40 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Actualización de estado de mercancías peligrosas
@@ -1661,39 +1912,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:36:13 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Status materiałów niebezpiecznych (hazmat)
@@ -1714,39 +1965,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:35:04 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>亚马逊卖家平台通知（请勿回复） &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>危险品状态更新</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  危险品状态更新
@@ -1794,39 +2045,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:28:59 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Statusuppdatering för farligt gods</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Statusuppdatering för farligt gods
@@ -1848,39 +2099,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:03:40 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Aggiornamento dello stato delle merci pericolose
@@ -1901,39 +2152,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:03:04 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Update van status gevaarlijke goederen</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Update van status gevaarlijke goederen
@@ -1954,39 +2205,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 04:15:54 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-08-27</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2010,39 +2261,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:35:04 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -2065,39 +2316,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:27:02 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Mise à jour du statut de matières dangereuses</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Mise à jour du statut de matières dangereuses
@@ -2118,39 +2369,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 04:59:33 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2166,39 +2417,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 12:15:45 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (tynmf1KRa8)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2218,39 +2469,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 05:20:43 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2266,39 +2517,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 05:46:43 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (m4n18h8HiD)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2323,39 +2574,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 05:00:42 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2371,39 +2622,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mon, 10 Aug 2026 09:16:35 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2419,39 +2670,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sun, 9 Aug 2026 14:33:13 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $126.79 in an attempt to settle your Amazon seller account balance.
@@ -2467,39 +2718,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Sun, 9 Aug 2026 04:49:49 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2515,39 +2766,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sat, 8 Aug 2026 14:11:22 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2568,39 +2819,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sat, 8 Aug 2026 05:00:20 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2616,39 +2867,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 17:55:17 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2669,39 +2920,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 04:52:01 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2717,39 +2968,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 17:19:22 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (PLBovnqz6i)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2769,39 +3020,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 05:43:06 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2817,39 +3068,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 04:57:39 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2865,39 +3116,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 16:27:49 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (3rwPw0NlBZ)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2917,39 +3168,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 04:52:33 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2965,39 +3216,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 04:46:25 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3013,39 +3264,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 04:49:15 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3061,39 +3312,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 09:23:20 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3109,39 +3360,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 19:42:31 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (YsvR7aqoWy)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3166,39 +3417,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 07:19:03 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (8AOhKJjKS4)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3218,39 +3469,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 05:45:50 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3266,39 +3517,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:56:25 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Amazon.sa" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been successfully updated</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been successfully updated
@@ -3314,39 +3565,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:49:41 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Amazon.fr" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Account Protection</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon Seller Account Protection
@@ -3363,39 +3614,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:48:37 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Amazon.ae" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been successfully updated</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been successfully updated
@@ -3411,39 +3662,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:43:00 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been updated successfully</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been updated successfully
@@ -3459,39 +3710,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:38:29 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been updated successfully</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been updated successfully
@@ -3507,39 +3758,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 14:56:26 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3560,39 +3811,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 05:51:10 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3608,39 +3859,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 09:53:48 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (WXuXOpUPId)</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3665,39 +3916,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 06:03:52 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3713,39 +3964,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Jul 2026 16:41:05 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (ckaicj9NPD)</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3765,39 +4016,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Jul 2026 09:48:04 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3813,39 +4064,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Jul 2026 04:57:36 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3861,39 +4112,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Jul 2026 20:49:44 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (1pqaY5uvK2)</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3918,39 +4169,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Jul 2026 14:44:02 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $63.02 in an attempt to settle your Amazon seller account balance.
@@ -3966,39 +4217,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Jul 2026 04:57:25 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4014,39 +4265,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 05:07:54 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4062,39 +4313,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 16:10:45 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been updated successfully</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been updated successfully
@@ -4110,39 +4361,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 10:35:17 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Zx1U3/hDuM)</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4162,39 +4413,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 05:01:14 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4210,39 +4461,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 05:03:32 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4258,135 +4509,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 21 Jul 2026 09:30:25 +0000</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfillment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
-- T</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 21 Jul 2026 04:57:37 +0000</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Jul 2026 06:15:19 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>【官方提示】请尽快通过您的欧洲站卖家资质KYC审核，以保证正常销售</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">账户注册
 															资质审查
@@ -4419,40 +4574,40 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 11:09:39 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Verstrek KYC-verificatie binnen 45 dagen om beperkingen te
  voorkomen</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Verstrek KYC-verificatie binnen 45 dagen om beperkingen te voorkomen
@@ -4471,39 +4626,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 10:52:41 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Provide KYC verification within 45 days to avoid restrictions</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Provide KYC verification within 45 days to avoid restrictions
@@ -4522,39 +4677,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 09:42:14 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Provide KYC verification within 45 days to avoid restrictions</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Provide KYC verification within 45 days to avoid restrictions
@@ -4573,39 +4728,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 09:24:08 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Fournissez une vérification KYC sous 45 jours pour éviter les restrictions</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Fournissez une vérification KYC sous 45 jours pour éviter les restrictions
@@ -4621,159 +4776,40 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>KYC审核类</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 21 Jul 2026 08:07:04 +0000</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>Know Your Customer (KYC) verification process support</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>96
- Pending Know Your Customer (KYC) account verification
- Hello,
- We are conducting a review of your Amazon Payments Account. We need additional information or documents to continue with your account verification. In accordance with regulations, you must complete an account verification process. Please go to the Identity Information page to provide the required information or documents:
- Submit documentation
- In some cases, we will send a notification that outlines the details of the request related to your Amazon Payments account. Please check the most recent performance notifications starting with the subject [Action Required]: Performance Notifications .
- What happens next?
- Once you have provided the requested information or documents, we will continue with your account verification. Please continue to proactively check the performance notifications or emails to understand if further information or documents are needed from you.
- Once the verification is complete, you will receive a performance notification and email advising you of the result.
- We’re here to help.
- If you have any questions, you can contact us at any time via Amazon Selling Partner Support .
- For more informa</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>KYC审核类</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 21 Jul 2026 07:52:22 +0000</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>96
-[需要采取的操作] 需要您的“我要开店”付款账户的相关信息
- [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
- 您好！
-此次联系您是因为我们需要一些其他文件才能继续验证您的账户。
-提供经过修改或篡改的文件可能会导致账户被永久关闭。
-我们仅允许修改银行对账单等文件，以遮挡付款余额等详细信息。
-如果我未采取措施或者不提供所需的信息/文件，会怎么样？
-自我们首次与您联系要求您采取措施或提供完成验证所需的所有文件和信息之日起，您总共有 60 天的时间来提供这些文件和信息。我们审核和验证您采取措施后的结果的时间或验证信息的时间不会计入给您的 60 天期限。
-如果您未能在 60 天内采取措施或提供要求的信息，您的商品将被暂时停售，并且您的提现功能将被暂时停用，直到完成验证为止。
-如果自我们首次联系您之日起已超过 60 天，则您的付款可能已被冻结，您的商品可能已被停售。在您提供要求的信息或文件且您的账户得到验证之前，您的付款将继续处于冻结状态，您的商品将继续处于停售状态。
-为什么会发生这种情况？
-您之前提供的银行账户所有权证明文件不足以完成验证流程，因为它它并未体现您账户上注册的**完整**公司名称。
-我需要提供哪种类型的文件？
--- 目前在卖家平台中输入为存款方式的其中2个银行账户的银行对账单或银行资信证明的扫描件：以 *29 和 *91 结尾的账号。
-如何处理这种情况？
-确保文件符合以下标准：
--- 文件必须是在最近 180 天内开具的。
--- 文件必须显示银行账号、银行徽标和账户持有者姓名。
--- 如果您以公司形式开展业务，则您的银行账户必须为公司账户。
--- 请务必确保文件清晰易读。
--- 文件不能是屏幕截图。
--- 文件必须使用我们支持的语言之一。我们支持以下语言：英语、中文、丹麦语、荷兰语、德语、意大利语、西班牙语、瑞典语、法语、土耳其语、波兰语、葡萄牙语、阿拉伯语、印地语、泰米尔语、越南语、泰语、韩语和日语。如果原始文件使用的不是我们支持的语言，请同时提供原始文件和翻译文件。
-我如何提供这些信息？
-请完成以下步骤，在卖家平台的“银行账户信息”部分更新您的银行账户信息：
-https://sellercentral-europe.amazon.com/sw/AccountInfo/DepositMethodView/step/DepositMethodView
-1.单击“更换存款方式”。
-2.在新出现的页面上，单击“添加新的存款方式”，并提供您尝试注册的银行账户的详细信息。
-3.单击“设置存款方式”。
-4.单击“验证账户”。
-5.转至卖家平台的“身份信息”部分：
-https://sellercentral-europe.amazon.com/sw/SSR/BusinessKYCInfo/spaDashboard
-6.按照相关提示上传要求提供的文</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 13:25:55 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Did you catch Mary Beth's message? Early-bird extension ends August
  29</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-07/7z543yq/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z543yt/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
@@ -4787,39 +4823,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 15:01:57 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4836,39 +4872,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4888,39 +4924,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 13:10:07 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Hear from sellers who've been to Accelerate—92.9% of sellers said it was worth it</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-11/7z56gp4/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z56gp7/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
@@ -4935,39 +4971,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 12:45:09 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Mary Beth Westmoreland invites you to Amazon Accelerate 2026</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-07/7z543zx/6824284947/h/IMGEB96CBgyW2DY04pRCmrOMWOWCmWx4Su6ckkT2afE)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z54411/6824284947/h/IMGEB96CBgyW2DY04pRCmrOMWOWCmWx4Su6ckkT2afE)
@@ -4980,39 +5016,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 11:39:46 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5029,39 +5065,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 11:39:19 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5081,39 +5117,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sun, 9 Aug 2026 14:20:11 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5133,39 +5169,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 23:31:39 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5185,39 +5221,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 15:18:33 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5237,39 +5273,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 15:18:03 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5286,39 +5322,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 15:17:38 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5338,39 +5374,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 15:49:22 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.36. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -5384,39 +5420,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 15:22:13 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5440,39 +5476,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 12:59:47 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5489,39 +5525,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 12:39:35 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Final week of early-bird pricing for Amazon Accelerate 2026—ends August 8</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-29/7z4ytv7/6806510535/h/ebUC-rn_gdmnOZgc0Tgqz8DiEn0AwvkMsQeazFirtjo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4ytvb/6806510535/h/ebUC-rn_gdmnOZgc0Tgqz8DiEn0AwvkMsQeazFirtjo)
@@ -5540,39 +5576,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 12:14:10 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5592,39 +5628,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 12:13:54 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5641,39 +5677,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 09:02:05 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Managing compliance across Europe? There's a simpler way.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Managing compliance across Europe? There's a simpler way.
  96
@@ -5683,39 +5719,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 12:51:30 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends August 8. Save $100 before the price goes up</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-29/7z4ytt4/6801785250/h/cuj5ZID4pxnaoQxnGKVediz6maB8MtzjCTkMytKZvg4)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4ytt7/6801785250/h/cuj5ZID4pxnaoQxnGKVediz6maB8MtzjCTkMytKZvg4)
@@ -5732,39 +5768,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 14:27:09 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5784,39 +5820,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 12:05:29 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Get 1:1 guidance from Amazon experts. Book your Seller Café appointment now</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-27/7z4wb13/6798182481/h/05AL5iRkNxOUgud3Z_einTRfylmI-j5cIlGQkJP8RGs)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4wb16/6798182481/h/05AL5iRkNxOUgud3Z_einTRfylmI-j5cIlGQkJP8RGs)
@@ -5832,39 +5868,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 06:58:29 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your information is verified – Start selling on Amazon now</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Seller,
@@ -5886,39 +5922,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 14:44:59 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5935,39 +5971,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 14:36:09 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5987,39 +6023,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 13:50:18 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Your information is verified – Start selling on Amazon now</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Seller,
@@ -6041,40 +6077,40 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 12:05:03 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Airline discounts and $100 off registration. Available for a limited
  time</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-20/7z4slz6/6793898954/h/insOo6D5kr2g-YQAHmot70JWv4JNrnk-FJT9rhAtCXc)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4slz9/6793898954/h/insOo6D5kr2g-YQAHmot70JWv4JNrnk-FJT9rhAtCXc)
@@ -6092,39 +6128,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 08:56:50 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Your information is verified – Start selling on Amazon now</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Seller,
@@ -6146,39 +6182,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Jul 2026 14:21:34 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6195,39 +6231,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Jul 2026 14:21:01 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6247,39 +6283,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Jul 2026 14:20:18 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6299,39 +6335,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Jul 2026 13:57:00 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6351,39 +6387,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 23:31:38 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6403,39 +6439,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 14:04:10 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6452,39 +6488,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 14:00:39 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6504,39 +6540,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 11:45:44 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>请在 45 天内提供“了解您的客户”验证，以避免受到限制</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  请在 45 天内提供“了解您的客户”验证，以避免受到限制
@@ -6585,39 +6621,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 11:27:26 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Proporciona los datos del proceso de verificación de la identidad del cliente en un plazo de 45 días para evitar restricciones</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Proporciona los datos del proceso de verificación de la identidad del cliente en un plazo de 45 días para evitar restricciones
@@ -6633,39 +6669,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 10:34:58 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>W ciągu 45 dni prześlij informacje na potrzeby weryfikacji w ramach procedury „Poznaj swojego klienta”, aby uniknąć ograniczeń</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  W ciągu 45 dni prześlij informacje na potrzeby weryfikacji w ramach procedury „Poznaj swojego klienta”, aby uniknąć ograniczeń
@@ -6681,39 +6717,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 10:18:19 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Tillhandahåll kundkännedomsverifiering inom 45 dagar för att undvika begränsningar</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Tillhandahåll kundkännedomsverifiering inom 45 dagar för att undvika begränsningar
@@ -6732,39 +6768,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 10:01:15 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Completa la verifica entro 45 giorni per evitare restrizioni</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Completa la verifica entro 45 giorni per evitare restrizioni
@@ -6780,39 +6816,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 09:07:51 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>请在 45 天内提供“了解您的客户”验证，以避免受到限制</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  请在 45 天内提供“了解您的客户”验证，以避免受到限制
@@ -6861,39 +6897,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 14:51:16 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -6909,39 +6945,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 14:00:14 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6961,39 +6997,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 12:14:46 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Getting to Accelerate just got more affordable</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-20/7z4sm1d/6783180395/h/9SAIODqFYxt9XXAbJGvHdl3Qa8teVnFPPUtWgSPQ3R8)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4sm1h/6783180395/h/9SAIODqFYxt9XXAbJGvHdl3Qa8teVnFPPUtWgSPQ3R8)
@@ -7010,39 +7046,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 14:43:36 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7062,39 +7098,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 14:42:48 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7111,58 +7147,6 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 21 Jul 2026 13:57:14 +0000</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement attempted
-Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
-On 07/21/26 13:57 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
- 467.73.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon Store,
-Amazon Services
-Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
@@ -7181,7 +7165,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Thu, 13 Aug 2026 04:08:25 +0000</t>
+          <t>Thu, 13 Aug 2026 16:08:49 +0000</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7196,6 +7180,56 @@
       </c>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 04:08:25 +0000</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7213,39 +7247,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 16:13:04 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Update tax information to prepare for UAE e-invoicing requirements</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Update tax information to prepare for UAE e-invoicing requirements
@@ -7260,39 +7294,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 17:07:34 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7310,39 +7344,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 16:07:16 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7361,39 +7395,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Mon, 10 Aug 2026 16:27:47 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Canada &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Your Tax Obligations on Amazon.ca</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 Your Tax Obligations on Amazon.ca
@@ -7411,39 +7445,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Mon, 10 Aug 2026 11:54:13 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -7459,39 +7493,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 18:48:57 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7510,39 +7544,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 17:04:28 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour les ventes sur Amazon.fr |
 Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales
@@ -7555,39 +7589,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 13:27:26 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7606,39 +7640,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 19:14:34 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Zwrot kosztów zgodności z wymogami w zakresie opakowań w ramach ROP</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Rozpocznij rejestrację w ramach ROP przed 12 sierpnia, aby uzyskać częściowy zwrot kosztów w Szwecji i Polsce
@@ -7655,39 +7689,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 18:39:18 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7706,39 +7740,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Wed, 5 Aug 2026 12:58:13 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>EPR Pay on Behalf charges for 2025 Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -7757,39 +7791,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 18:16:42 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7808,39 +7842,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 17:58:25 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7859,39 +7893,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:55:58 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7910,39 +7944,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:41:59 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7961,39 +7995,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 15:45:25 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -8020,39 +8054,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 09:15:08 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8070,39 +8104,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 03:48:43 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -8130,39 +8164,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 00:32:40 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8180,39 +8214,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 00:25:49 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8230,39 +8264,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 16:15:51 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -8280,39 +8314,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 15:08:44 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -8331,39 +8365,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 15:08:23 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Action required: Notification of ASIN removal</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello xiao jianming,
@@ -8379,39 +8413,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:23:21 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8429,39 +8463,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:17:26 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8479,39 +8513,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Action required: Notification of ASIN removal</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8527,39 +8561,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:10:39 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Action required: Notification of ASIN removal</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8575,40 +8609,40 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 09:26:45 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.de" &lt;toys-safety-mv@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13104358872] SELLER: A1UYGOR4ZW45MU, ASIN: B0F13M1H6F,
  MARKETPLACE: 4 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13104358872] SELLER: A1UYGOR4ZW45MU, ASIN: B0F13M1H6F, MARKETPLACE: 4 - PS - APPEAL
@@ -8633,39 +8667,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 14:11:48 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>You asked for smarter AI tools. We're delivering at Accelerate 2026</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-22/7z4t8v9/6787753082/h/IGusOwCMHYF897jTLiEldN8I_908U5ToWDqeOf0umps)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4t8vd/6787753082/h/IGusOwCMHYF897jTLiEldN8I_908U5ToWDqeOf0umps)
@@ -8681,39 +8715,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 23:12:37 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8732,39 +8766,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 12:38:11 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -8780,39 +8814,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 09:21:24 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13075958512] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13075958512] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规
@@ -8847,39 +8881,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 23:10:13 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8898,39 +8932,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 19:11:54 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8948,39 +8982,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 19:09:21 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8995,54 +9029,6 @@
  If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
 -
  If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 21 Jul 2026 12:36:12 +0000</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon-Fulfilled Inventory - Action Required</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
-Please create a removal request for the ASIN(s) listed below to have your inventory sent to a location of your choice. If this inventory is not removed within 30 days of this notification (by 19/08/2026), we shall dispose of it in accordance with our FBA policies.
-For more information regarding the removal of this product, see the notification e-mail you received from our Seller Performance Team.
-Thank you for your prompt attention to this matter.
-Yours faithfully,
-Fulfilment by Amazon Team
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0F23SWF2P
- SPC-EUAmazon-1073125022066229</t>
         </is>
       </c>
     </row>
@@ -19657,74 +19643,6 @@
         </is>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B367" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C367" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D367" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 21 Jul 2026 05:44:42 +0000</t>
-        </is>
-      </c>
-      <c r="E367" s="2" t="inlineStr">
-        <is>
-          <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
-        </is>
-      </c>
-      <c r="F367" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【重要】西班牙VAT通知期延期指南。税号激活用时最长达37周，请立即行动以免影响销售 </t>
-        </is>
-      </c>
-      <c r="G367" s="2" t="inlineStr"/>
-      <c r="H367" s="2" t="inlineStr">
-        <is>
-          <t>西班牙延期政策更新：已过通知期也可发起申请
-			尊敬的 深圳市微海众信科技有限公司,
-			您收到这封邮件，是因为您是西班牙VAT增值税注册要求的潜在受影响卖家。
-			为帮助您顺利推进合规，亚马逊整理了《西班牙增值税合规要求、延期规则介绍及卖家行动指南》，内容涵盖：
-			● 西班牙增值税合规要求及不合规影响
-			● 完整西班牙增值税号流程及材料清单
-			● 亚马逊通知期延期规则及申请指导（政策更新）
-			● 常见问题（如库存影响、滞留库存处理等）
-			扫描下方二维码下载完整行动指南
-			下载二维码
-			本邮件重点提示其中热点内容：通知期延期申请规则、操作流程、关键提醒。
-			一、什么情况可以申请延期？
-			当您的亚马逊账户健康页面显示西班牙的'欧洲增值税注册要求'通知，但您正在办理西班牙VIES增值税注册或恢复VIES增值税号有效性，且需要更多时间完成合规流程时，您可能有资格申请最长150天的延期。
-			关键更新：根据亚马逊最新的政策，如果您目前还没有上传西班牙VIES欧盟税号（包括只上传了西班牙本地税号），即使您的西班牙通知期已经过期，您仍然有机会申请延期，审核通过后可重新启用FBA并获得西班牙本地配送费率福利。
-			二、如何申请通知期延期？两种操作路径
-			情况一：账户健康页面显示'我了解政策要求，希望申请更多时间以满足要求'选项
-			第一步：前往卖家平台，账户健康页面
-			第二步：在'优先操作'部分点击'欧洲增值税注册要求'
-			第三步：点击'提交所需文件'选项
-			第四步：选择'我了解政策要求，希望请求更多时间以满足相关要求或提供证据证明我不需要满足此要求'
-			第五步：上传附件'036表单'
-			第六步：点击'提交'
-			【如需查看图文指导，可通过邮件上方二维码下载查看完整行动手册】
-			情况二：账户健康页面未显示'我了解政策要求，希望申请更多时间以满足要求'选项
-			卖家需自行发送邮件申请，邮件标题为：'申请西班牙税号通知期延期'，正文须包含以下信息：
-			● 您的卖家记号（Merchant Token）
-			● 036表单附件
-			发送邮箱地址：vas-seller-extension-appeals@amazon.co.uk
-			亚马逊将在5个工作日内审核您的提交并通知您后续步骤。
-			关于036表单，请注意：036表单可在您的VIES激活申请提交后，向您的西班牙税务服务商索取。提交延期申请时，请确保036表单文件有效，且文件中的公司名称、增值税号与您卖家平台账户中的信息一致。
-			*本内容基于亚马逊服务商网络（SPN）增值税服务商提供的数据整理，仅供参考。不代表对亚马逊任何相关法律、法规、政策或要求的解读，亦不构成税务或法律建议。具体流程因西班牙增值税服务商及您的个人情况而异。请咨询</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
